--- a/Excel/ExclusiveSuitConfig.xlsx
+++ b/Excel/ExclusiveSuitConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
   <si>
     <t>ID</t>
   </si>
@@ -84,6 +89,12 @@
   </si>
   <si>
     <t>神话全属性+10%</t>
+  </si>
+  <si>
+    <t>虚无套装</t>
+  </si>
+  <si>
+    <t>神话全属性+20%</t>
   </si>
 </sst>
 </file>
@@ -1250,7 +1261,32 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="27" customHeight="1"/>
+    <row r="10" customFormat="1" ht="27" customHeight="1" spans="1:10">
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>1025</v>
+      </c>
+      <c r="G10">
+        <v>1030</v>
+      </c>
+      <c r="H10">
+        <v>94</v>
+      </c>
+      <c r="I10">
+        <v>20</v>
+      </c>
+      <c r="J10" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="11" customFormat="1" ht="27" customHeight="1"/>
     <row r="12" customFormat="1" ht="27" customHeight="1"/>
     <row r="13" customFormat="1" ht="27" customHeight="1"/>
